--- a/docs/xlsx/jobs-2026-08-22.xlsx
+++ b/docs/xlsx/jobs-2026-08-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,48 @@
     <t>Link</t>
   </si>
   <si>
+    <t>CMS Early Childhood Coordinator</t>
+  </si>
+  <si>
+    <t>Brooklyn Conservatory of Music</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/693d4e458b954f54b0a0c69647ae604d-cms-early-childhood-coordinator-brooklyn-conservatory-of-music-kings-county</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>OSG</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dfe921129bc84a93a5b6104ccf71cf7d-director-of-development-osg-arlington</t>
+  </si>
+  <si>
     <t>Director, Marketing and Communication</t>
   </si>
   <si>
@@ -49,9 +91,6 @@
     <t>Glen Burnie, Maryland</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 65000.00 - 85000.00/year</t>
   </si>
   <si>
@@ -59,6 +98,42 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/db7f756ba47c469ca42aa4700c5b2700-director-marketing-and-communication-national-cryptologic-foundation-glen-burnie</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Coalition for African Americans in the Performing Arts</t>
+  </si>
+  <si>
+    <t>Remote (national harbor, Maryland)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb3692c1effa4968a2f4f236d5426655-executive-director-coalition-for-african-americans-in-the-performing-arts-national-harbor</t>
+  </si>
+  <si>
+    <t>Marketing Manager (San Francisco or Los Angeles)</t>
+  </si>
+  <si>
+    <t>Women's Audio Mission</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1eac41f2cb97404fa7e43054d2054214-marketing-manager-san-francisco-or-los-angeles-womens-audio-mission-san-francisco</t>
   </si>
   <si>
     <t>Operations Coordinator</t>
@@ -576,7 +651,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -649,39 +724,131 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -690,6 +857,10 @@
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
